--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-01).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-01).xlsx
@@ -935,31 +935,31 @@
     <t>214</t>
   </si>
   <si>
-    <t>22</t>
+    <t>21</t>
   </si>
   <si>
-    <t>R$ 5.787,37</t>
+    <t>R$ 5.803,27</t>
   </si>
   <si>
-    <t>61.3</t>
+    <t>61.4</t>
   </si>
   <si>
     <t>40.4</t>
   </si>
   <si>
-    <t>5.98</t>
+    <t>5.97</t>
   </si>
   <si>
     <t>21.0</t>
   </si>
   <si>
-    <t>8.3</t>
+    <t>8.4</t>
   </si>
   <si>
     <t>6.4</t>
   </si>
   <si>
-    <t>33.6%</t>
+    <t>33.9%</t>
   </si>
   <si>
     <t>18.0%</t>
@@ -10175,7 +10175,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -10205,18 +10205,30 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
+      <c r="M58" s="5">
+        <v>8839.7800000000007</v>
+      </c>
+      <c r="N58" s="6">
+        <v>94</v>
+      </c>
       <c r="O58" s="6">
         <v>79</v>
       </c>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
+      <c r="P58" s="7">
+        <v>3.8292118279569891</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>19.676370886075947</v>
+      </c>
+      <c r="R58" s="8">
+        <v>9.1102564102564099</v>
+      </c>
       <c r="S58" s="8">
         <v>7</v>
       </c>
-      <c r="T58" s="9"/>
+      <c r="T58" s="9">
+        <v>0.29113924050632911</v>
+      </c>
       <c r="U58" s="9">
         <v>0.13924050632911392</v>
       </c>
